--- a/public/templates/examples/A-029-PolicyReviewApprovalLog-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-029-PolicyReviewApprovalLog-EXAMPLE-M.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -211,12 +211,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="552450" cy="552450"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -330,7 +330,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,7 +364,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-029-PolicyReviewApprovalLog-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-029-PolicyReviewApprovalLog-EXAMPLE-M.xlsx
@@ -4,19 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Aptos"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -129,6 +131,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -574,7 +582,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -766,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>0001</t>
@@ -787,10 +795,8 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
+      <c r="E12" s="12">
+        <v>45910</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
@@ -812,13 +818,11 @@
           <t>Annual review; no change</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
+      <c r="J12" s="12">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>0002</t>
@@ -839,10 +843,8 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
+      <c r="E13" s="12">
+        <v>45938</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -864,13 +866,11 @@
           <t>Clarified personal-device use</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1">
+      <c r="J13" s="12">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>0003</t>
@@ -891,10 +891,8 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
+      <c r="E14" s="12">
+        <v>45973</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
@@ -916,13 +914,11 @@
           <t>Added multifactor requirement for consoles</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
+      <c r="J14" s="12">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>0004</t>
@@ -943,10 +939,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
+      <c r="E15" s="12">
+        <v>46036</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -968,13 +962,11 @@
           <t>No change</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>2027-01-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
+      <c r="J15" s="12">
+        <v>46401</v>
+      </c>
+    </row>
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>0005</t>
@@ -995,10 +987,8 @@
           <t>1.2</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
+      <c r="E16" s="12">
+        <v>46064</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -1020,13 +1010,11 @@
           <t>Raised minimum length</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>2027-02-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
+      <c r="J16" s="12">
+        <v>46429</v>
+      </c>
+    </row>
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>0006</t>
@@ -1047,10 +1035,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
+      <c r="E17" s="12">
+        <v>46092</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -1072,13 +1058,11 @@
           <t>No change</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>2027-03-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
+      <c r="J17" s="12">
+        <v>46457</v>
+      </c>
+    </row>
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>0007</t>
@@ -1099,10 +1083,8 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
+      <c r="E18" s="12">
+        <v>46120</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
@@ -1124,10 +1106,8 @@
           <t>No change</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>2027-04-08</t>
-        </is>
+      <c r="J18" s="12">
+        <v>46485</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1"/>
@@ -1191,10 +1171,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D25" s="13">
+        <v>46174</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -1213,10 +1191,8 @@
           <t>Anthony Reyes</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D26" s="13">
+        <v>46174</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1"/>
@@ -1264,7 +1240,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1">
+    <row r="36" ht="34.7" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Version</t>
@@ -1286,16 +1262,14 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1">
+    <row r="37" ht="34.7" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
+      <c r="B37" s="12">
+        <v>45809</v>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
@@ -1308,16 +1282,14 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="17" customHeight="1">
+    <row r="38" ht="50.5" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="B38" s="12">
+        <v>46174</v>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
@@ -1355,7 +1327,8 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>